--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영_인쇄용.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영_인쇄용.xlsx
@@ -552,11 +552,10 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당 실명은 지정되지 않아 각 시트 제목의 [담당자 지정 후 이름 기재]로 비어 있습니다. 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-01~A-14 대체자는 이광재 부장입니다(A-15·A-16 대체자는 미지정). 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -600,7 +599,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-10-29</t>
+          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-29</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -625,7 +624,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-10-30</t>
+          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-30</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -650,7 +649,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-02</t>
+          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-02</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -675,7 +674,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-04</t>
+          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -700,7 +699,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-04</t>
+          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -750,7 +749,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-05</t>
+          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-05</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -800,7 +799,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-06</t>
+          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -875,7 +874,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-06</t>
+          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -950,7 +949,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-10</t>
+          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1025,7 +1024,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-12</t>
+          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1075,7 +1074,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-12</t>
+          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1125,7 +1124,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-10</t>
+          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1175,7 +1174,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1250,7 +1249,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: [담당자 지정 후 이름 기재] · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1366,7 +1365,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1671,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1680,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2044,7 +2041,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2291,7 +2287,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2546,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2552,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2917,7 +2911,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3162,7 +3155,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3341,7 +3333,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-11 2026 내부심사 시행 및 부적합 종결 — 담당 역할: 내부심사 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3344,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3673,7 +3664,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4403,7 +4393,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4659,7 +4648,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -4709,7 +4697,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -4759,7 +4746,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -4802,7 +4788,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -4891,7 +4876,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 권고일 2026-11-12</t>
+          <t>A-12 경영검토 실적·경영진 승인 — 담당 역할: 경영진/환경 · 담당자: 김흥수 이사 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4887,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5214,7 +5198,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5556,7 +5539,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 권고일 2026-11-12</t>
+          <t>A-13 기안서 최종 결재·송금·증빙 — 담당 역할: 회계/기안 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-12</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5550,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5887,7 +5869,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6081,7 +6062,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-11-10</t>
+          <t>A-14 이전 인증기관 지적·개선조치 종료 근거 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-10</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6073,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6374,7 +6354,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6592,7 +6571,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6870,7 +6848,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7441,7 +7418,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7657,7 +7633,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7960,7 +7935,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 권고일 2026-10-29</t>
+          <t>A-03 최신 인원/조직도·교대현황 확정 — 담당 역할: 인사/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7946,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8330,7 +8304,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8874,7 +8847,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 권고일 2026-10-30</t>
+          <t>A-04 현행 EMS 환경매뉴얼·절차서·양식 및 개정목록 제출 — 담당 역할: 환경관리 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8858,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9277,7 +9249,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 권고일 2026-11-02</t>
+          <t>A-05 공정별 환경측면·중대한 측면 평가 실제 기록 제출 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-02</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9260,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9851,7 +9822,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 권고일 2026-11-04</t>
+          <t>A-06 적용법규·인허가·신고·준수평가 최신 기록 — 담당 역할: 환경/설비 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9833,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10322,7 +10292,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 권고일 2026-11-04</t>
+          <t>A-07 최근 1년 폐기물 처리·보관·위탁 증빙 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-04</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10303,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10694,7 +10663,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10974,7 +10942,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 권고일 2026-11-05</t>
+          <t>A-08 화학물질·MSDS·용기표시·누출관리 — 담당 역할: 환경/생산 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-05</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10953,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영_인쇄용.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A03-A16_통합요청표_20261028_담당자반영_인쇄용.xlsx
@@ -552,10 +552,11 @@
     <row r="2" ht="62" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-01~A-14 대체자는 이광재 부장입니다(A-15·A-16 대체자는 미지정). 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
-        </is>
-      </c>
-    </row>
+          <t>NQA 갱신심사 2026-11-19~20 (ISO 14001:2015 갱신만 진행, 2026 전환 미진행: 사용자 결정 2026-10-28). 담당자는 2026-10-28 담당자 지정표 기준으로 각 시트 제목에 기재했고, A-03~A-16 대체자는 이광재 부장입니다. 시행 전 기록은 "미확인", 소급 작성 금지. 노란 칸이 입력 칸이며 시트 이름을 누르면 해당 시트로 이동합니다. A-01·A-02는 완료(인증서 스캔본 확보, NQA 유선 회신)로 별도 표(ISO14001_증빙수집요청표_20261028_v4.xlsx)에 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1174,7 +1175,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 대체자: 이광재 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1249,7 +1250,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1365,6 +1366,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1680,6 +1682,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2041,6 +2044,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2287,6 +2291,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2552,6 +2557,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2911,6 +2917,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3155,6 +3162,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3344,6 +3352,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3664,6 +3673,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4393,6 +4403,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4648,6 +4659,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -4697,6 +4709,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -4746,6 +4759,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -4788,6 +4802,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -4887,6 +4902,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5198,6 +5214,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5550,6 +5567,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -5869,6 +5887,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6073,6 +6092,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6354,6 +6374,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6560,7 +6581,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 권고일 2026-11-16</t>
+          <t>A-15 현장 동선점검·작업자 인터뷰 — 담당 역할: 생산/설비/환경 · 담당자: 지성규 부장 · 대체자: 이광재 부장 · 권고일 2026-11-16</t>
         </is>
       </c>
     </row>
@@ -6571,6 +6592,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -6848,6 +6870,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7418,6 +7441,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7622,7 +7646,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 권고일 2026-11-17</t>
+          <t>A-16 심사대응 인원·장소·자료폴더 지정 — 담당 역할: 심사총괄 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-17</t>
         </is>
       </c>
     </row>
@@ -7633,6 +7657,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7946,6 +7971,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8304,6 +8330,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -8858,6 +8885,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9260,6 +9288,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9833,6 +9862,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10303,6 +10333,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10663,6 +10694,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -10953,6 +10985,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
